--- a/data/input/feed/icsg/current/conc.xlsx
+++ b/data/input/feed/icsg/current/conc.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Refining(Scrap input) maps to ER process; scrap input to electrolytic refining</t>
+          <t>Refining(Scrap input) maps to CFR: direct-to-refinery scrap — secondary refined production minus the smelter route (ADR 0021, ADR 0030)</t>
         </is>
       </c>
     </row>
